--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NORTH_CAROLINA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NORTH_CAROLINA_2024.xlsx
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C198">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C327">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C464">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C737">
